--- a/tests/regression_artifacts/downloads/email_03152025_RECEIPT/current/HAWB9600998-Declaration_combined.xlsx
+++ b/tests/regression_artifacts/downloads/email_03152025_RECEIPT/current/HAWB9600998-Declaration_combined.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Combined Invoices" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="OCR Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combined Invoices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OCR Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK76"/>
+  <dimension ref="A1:AK74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -794,14 +794,14 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>36049000</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>62034290</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       <c r="AJ2" s="2" t="n"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>36049000</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>36049000</t>
         </is>
       </c>
       <c r="G3" s="4" t="n"/>
@@ -950,7 +950,11 @@
       <c r="AH3" s="4" t="n"/>
       <c r="AI3" s="4" t="n"/>
       <c r="AJ3" s="4" t="n"/>
-      <c r="AK3" s="4" t="n"/>
+      <c r="AK3" s="4" t="inlineStr">
+        <is>
+          <t>36049000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n"/>
@@ -960,7 +964,7 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>36049000</t>
         </is>
       </c>
       <c r="G4" s="4" t="n"/>
@@ -1017,7 +1021,11 @@
       <c r="AH4" s="4" t="n"/>
       <c r="AI4" s="4" t="n"/>
       <c r="AJ4" s="4" t="n"/>
-      <c r="AK4" s="4" t="n"/>
+      <c r="AK4" s="4" t="inlineStr">
+        <is>
+          <t>36049000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -1034,7 +1042,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>HATS AND OTHER HEADGEAR, PLAITED OR MADE BY ASSEMBLING STRIPS</t>
+          <t>Headgear</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1046,7 +1054,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1167,7 +1175,11 @@
       <c r="AH6" s="4" t="n"/>
       <c r="AI6" s="4" t="n"/>
       <c r="AJ6" s="4" t="n"/>
-      <c r="AK6" s="4" t="n"/>
+      <c r="AK6" s="4" t="inlineStr">
+        <is>
+          <t>65040000</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
@@ -1234,7 +1246,11 @@
       <c r="AH7" s="4" t="n"/>
       <c r="AI7" s="4" t="n"/>
       <c r="AJ7" s="4" t="n"/>
-      <c r="AK7" s="4" t="n"/>
+      <c r="AK7" s="4" t="inlineStr">
+        <is>
+          <t>65040000</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n"/>
@@ -1301,7 +1317,11 @@
       <c r="AH8" s="4" t="n"/>
       <c r="AI8" s="4" t="n"/>
       <c r="AJ8" s="4" t="n"/>
-      <c r="AK8" s="4" t="n"/>
+      <c r="AK8" s="4" t="inlineStr">
+        <is>
+          <t>65040000</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -1450,7 +1470,6 @@
       <c r="AJ11" s="8" t="n"/>
       <c r="AK11" s="8" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="6" t="n"/>
@@ -1680,7 +1699,6 @@
       <c r="AJ17" s="6" t="n"/>
       <c r="AK17" s="6" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="6" t="n"/>
@@ -1776,7 +1794,6 @@
       <c r="AJ20" s="6" t="n"/>
       <c r="AK20" s="6" t="n"/>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="10" t="n"/>
@@ -1826,7 +1843,6 @@
       <c r="AJ22" s="10" t="n"/>
       <c r="AK22" s="10" t="n"/>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="12" t="n"/>
       <c r="B24" s="12" t="n"/>
@@ -2017,7 +2033,7 @@
       <c r="I28" s="13" t="n"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 62046290: 20% CET (45% of value)</t>
+          <t xml:space="preserve">  └ 62034290: 20% CET (45% of value)</t>
         </is>
       </c>
       <c r="K28" s="13" t="n"/>
@@ -2062,7 +2078,7 @@
       <c r="I29" s="13" t="n"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 65040000: 20% CET (55% of value)</t>
+          <t xml:space="preserve">  └ 65000090: 20% CET (55% of value)</t>
         </is>
       </c>
       <c r="K29" s="13" t="n"/>
@@ -2404,11 +2420,7 @@
           <t>H&amp;M</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>H &amp; M Hennes &amp; Mauritz L.P., 1600 River Road, Burlington, NJ 08016, USA</t>
-        </is>
-      </c>
+      <c r="AB35" s="2" t="n"/>
       <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>US</t>
@@ -2581,7 +2593,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>62044300</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -2593,11 +2605,11 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>—— (1 items)</t>
+          <t>—— (+1 more) (2 items)</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
@@ -2607,10 +2619,10 @@
         </is>
       </c>
       <c r="O38" s="3" t="n">
-        <v>20.99</v>
+        <v>19.49</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>20.99</v>
+        <v>38.98</v>
       </c>
       <c r="Q38" s="3">
         <f>O38*K38</f>
@@ -2640,7 +2652,7 @@
       <c r="AJ38" s="2" t="n"/>
       <c r="AK38" s="2" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>62044300</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2664,7 @@
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>62044300</t>
         </is>
       </c>
       <c r="G39" s="4" t="n"/>
@@ -2711,159 +2723,129 @@
       <c r="AJ39" s="4" t="n"/>
       <c r="AK39" s="4" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>62044300</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>15046495444</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>MARINE ELECTRONICS</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>85176200</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>85176200</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Siri (1 items)</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="n">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>71171900</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Siri</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="O40" s="3" t="n">
+      <c r="O40" s="5" t="n">
         <v>17.99</v>
       </c>
-      <c r="P40" s="3" t="n">
+      <c r="P40" s="5" t="n">
         <v>17.99</v>
       </c>
-      <c r="Q40" s="3">
+      <c r="Q40" s="5">
         <f>O40*K40</f>
         <v/>
       </c>
-      <c r="R40" s="3">
+      <c r="R40" s="5">
         <f>P40-Q40</f>
         <v/>
       </c>
-      <c r="S40" s="3" t="n"/>
-      <c r="T40" s="3" t="n"/>
-      <c r="U40" s="3" t="n"/>
-      <c r="V40" s="3" t="n"/>
-      <c r="W40" s="3" t="n"/>
-      <c r="X40" s="2" t="n"/>
-      <c r="Y40" s="2" t="n"/>
-      <c r="Z40" s="2" t="n"/>
-      <c r="AA40" s="2" t="n"/>
-      <c r="AB40" s="2" t="n"/>
-      <c r="AC40" s="2" t="n"/>
-      <c r="AD40" s="2" t="n"/>
-      <c r="AE40" s="2" t="n"/>
-      <c r="AF40" s="2" t="n"/>
-      <c r="AG40" s="2" t="n"/>
-      <c r="AH40" s="2" t="n"/>
-      <c r="AI40" s="2" t="n"/>
-      <c r="AJ40" s="2" t="n"/>
-      <c r="AK40" s="2" t="inlineStr">
-        <is>
-          <t>85176200</t>
+      <c r="S40" s="4" t="n"/>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
+      <c r="W40" s="4" t="n"/>
+      <c r="X40" s="4" t="n"/>
+      <c r="Y40" s="4" t="n"/>
+      <c r="Z40" s="4" t="n"/>
+      <c r="AA40" s="4" t="n"/>
+      <c r="AB40" s="4" t="n"/>
+      <c r="AC40" s="4" t="n"/>
+      <c r="AD40" s="4" t="n"/>
+      <c r="AE40" s="4" t="n"/>
+      <c r="AF40" s="4" t="n"/>
+      <c r="AG40" s="4" t="n"/>
+      <c r="AH40" s="4" t="n"/>
+      <c r="AI40" s="4" t="n"/>
+      <c r="AJ40" s="4" t="n"/>
+      <c r="AK40" s="4" t="inlineStr">
+        <is>
+          <t>71171900</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>85176200</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Siri</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="4" t="n"/>
-      <c r="M41" s="4" t="n"/>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O41" s="5" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="Q41" s="5">
-        <f>O41*K41</f>
-        <v/>
-      </c>
-      <c r="R41" s="5">
-        <f>P41-Q41</f>
-        <v/>
-      </c>
-      <c r="S41" s="4" t="n"/>
-      <c r="T41" s="4" t="n"/>
-      <c r="U41" s="4" t="n"/>
-      <c r="V41" s="4" t="n"/>
-      <c r="W41" s="4" t="n"/>
-      <c r="X41" s="4" t="n"/>
-      <c r="Y41" s="4" t="n"/>
-      <c r="Z41" s="4" t="n"/>
-      <c r="AA41" s="4" t="n"/>
-      <c r="AB41" s="4" t="n"/>
-      <c r="AC41" s="4" t="n"/>
-      <c r="AD41" s="4" t="n"/>
-      <c r="AE41" s="4" t="n"/>
-      <c r="AF41" s="4" t="n"/>
-      <c r="AG41" s="4" t="n"/>
-      <c r="AH41" s="4" t="n"/>
-      <c r="AI41" s="4" t="n"/>
-      <c r="AJ41" s="4" t="n"/>
-      <c r="AK41" s="4" t="n"/>
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>SUBTOTAL (GROUPED)</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="6" t="n"/>
+      <c r="O41" s="6" t="n"/>
+      <c r="P41" s="7">
+        <f>P35+P38</f>
+        <v/>
+      </c>
+      <c r="Q41" s="7">
+        <f>Q35+Q38</f>
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n"/>
+      <c r="S41" s="6" t="n"/>
+      <c r="T41" s="6" t="n"/>
+      <c r="U41" s="6" t="n"/>
+      <c r="V41" s="6" t="n"/>
+      <c r="W41" s="6" t="n"/>
+      <c r="X41" s="6" t="n"/>
+      <c r="Y41" s="6" t="n"/>
+      <c r="Z41" s="6" t="n"/>
+      <c r="AA41" s="6" t="n"/>
+      <c r="AB41" s="6" t="n"/>
+      <c r="AC41" s="6" t="n"/>
+      <c r="AD41" s="6" t="n"/>
+      <c r="AE41" s="6" t="n"/>
+      <c r="AF41" s="6" t="n"/>
+      <c r="AG41" s="6" t="n"/>
+      <c r="AH41" s="6" t="n"/>
+      <c r="AI41" s="6" t="n"/>
+      <c r="AJ41" s="6" t="n"/>
+      <c r="AK41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -2877,7 +2859,7 @@
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>SUBTOTAL (GROUPED)</t>
+          <t>SUBTOTAL (DETAILS)</t>
         </is>
       </c>
       <c r="K42" s="6" t="n"/>
@@ -2886,11 +2868,11 @@
       <c r="N42" s="6" t="n"/>
       <c r="O42" s="6" t="n"/>
       <c r="P42" s="7">
-        <f>P35+P38+P40</f>
+        <f>SUM(P35:P40)-P41</f>
         <v/>
       </c>
       <c r="Q42" s="7">
-        <f>Q35+Q38+Q40</f>
+        <f>SUM(Q35:Q40)-Q41</f>
         <v/>
       </c>
       <c r="R42" s="6" t="n"/>
@@ -2915,104 +2897,99 @@
       <c r="AK42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="n"/>
-      <c r="I43" s="6" t="n"/>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>SUBTOTAL (DETAILS)</t>
-        </is>
-      </c>
-      <c r="K43" s="6" t="n"/>
-      <c r="L43" s="6" t="n"/>
-      <c r="M43" s="6" t="n"/>
-      <c r="N43" s="6" t="n"/>
-      <c r="O43" s="6" t="n"/>
-      <c r="P43" s="7">
-        <f>SUM(P35:P41)-P42</f>
-        <v/>
-      </c>
-      <c r="Q43" s="7">
-        <f>SUM(Q35:Q41)-Q42</f>
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n"/>
-      <c r="S43" s="6" t="n"/>
-      <c r="T43" s="6" t="n"/>
-      <c r="U43" s="6" t="n"/>
-      <c r="V43" s="6" t="n"/>
-      <c r="W43" s="6" t="n"/>
-      <c r="X43" s="6" t="n"/>
-      <c r="Y43" s="6" t="n"/>
-      <c r="Z43" s="6" t="n"/>
-      <c r="AA43" s="6" t="n"/>
-      <c r="AB43" s="6" t="n"/>
-      <c r="AC43" s="6" t="n"/>
-      <c r="AD43" s="6" t="n"/>
-      <c r="AE43" s="6" t="n"/>
-      <c r="AF43" s="6" t="n"/>
-      <c r="AG43" s="6" t="n"/>
-      <c r="AH43" s="6" t="n"/>
-      <c r="AI43" s="6" t="n"/>
-      <c r="AJ43" s="6" t="n"/>
-      <c r="AK43" s="6" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="n"/>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>GROUP VERIFICATION</t>
         </is>
       </c>
-      <c r="K44" s="8" t="n"/>
-      <c r="L44" s="8" t="n"/>
-      <c r="M44" s="8" t="n"/>
-      <c r="N44" s="8" t="n"/>
-      <c r="O44" s="8" t="n"/>
-      <c r="P44" s="9">
-        <f>P42-P43</f>
-        <v/>
-      </c>
-      <c r="Q44" s="9">
-        <f>Q42-Q43</f>
-        <v/>
-      </c>
-      <c r="R44" s="8" t="n"/>
-      <c r="S44" s="8" t="n"/>
-      <c r="T44" s="8" t="n"/>
-      <c r="U44" s="8" t="n"/>
-      <c r="V44" s="8" t="n"/>
-      <c r="W44" s="8" t="n"/>
-      <c r="X44" s="8" t="n"/>
-      <c r="Y44" s="8" t="n"/>
-      <c r="Z44" s="8" t="n"/>
-      <c r="AA44" s="8" t="n"/>
-      <c r="AB44" s="8" t="n"/>
-      <c r="AC44" s="8" t="n"/>
-      <c r="AD44" s="8" t="n"/>
-      <c r="AE44" s="8" t="n"/>
-      <c r="AF44" s="8" t="n"/>
-      <c r="AG44" s="8" t="n"/>
-      <c r="AH44" s="8" t="n"/>
-      <c r="AI44" s="8" t="n"/>
-      <c r="AJ44" s="8" t="n"/>
-      <c r="AK44" s="8" t="n"/>
-    </row>
-    <row r="45"/>
+      <c r="K43" s="8" t="n"/>
+      <c r="L43" s="8" t="n"/>
+      <c r="M43" s="8" t="n"/>
+      <c r="N43" s="8" t="n"/>
+      <c r="O43" s="8" t="n"/>
+      <c r="P43" s="9">
+        <f>P41-P42</f>
+        <v/>
+      </c>
+      <c r="Q43" s="9">
+        <f>Q41-Q42</f>
+        <v/>
+      </c>
+      <c r="R43" s="8" t="n"/>
+      <c r="S43" s="8" t="n"/>
+      <c r="T43" s="8" t="n"/>
+      <c r="U43" s="8" t="n"/>
+      <c r="V43" s="8" t="n"/>
+      <c r="W43" s="8" t="n"/>
+      <c r="X43" s="8" t="n"/>
+      <c r="Y43" s="8" t="n"/>
+      <c r="Z43" s="8" t="n"/>
+      <c r="AA43" s="8" t="n"/>
+      <c r="AB43" s="8" t="n"/>
+      <c r="AC43" s="8" t="n"/>
+      <c r="AD43" s="8" t="n"/>
+      <c r="AE43" s="8" t="n"/>
+      <c r="AF43" s="8" t="n"/>
+      <c r="AG43" s="8" t="n"/>
+      <c r="AH43" s="8" t="n"/>
+      <c r="AI43" s="8" t="n"/>
+      <c r="AJ43" s="8" t="n"/>
+      <c r="AK43" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="n"/>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INTERNAL FREIGHT</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="n"/>
+      <c r="L45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="6" t="n"/>
+      <c r="O45" s="6" t="n"/>
+      <c r="P45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="7" t="n"/>
+      <c r="R45" s="6" t="n"/>
+      <c r="S45" s="6" t="n"/>
+      <c r="T45" s="6" t="n"/>
+      <c r="U45" s="6" t="n"/>
+      <c r="V45" s="6" t="n"/>
+      <c r="W45" s="6" t="n"/>
+      <c r="X45" s="6" t="n"/>
+      <c r="Y45" s="6" t="n"/>
+      <c r="Z45" s="6" t="n"/>
+      <c r="AA45" s="6" t="n"/>
+      <c r="AB45" s="6" t="n"/>
+      <c r="AC45" s="6" t="n"/>
+      <c r="AD45" s="6" t="n"/>
+      <c r="AE45" s="6" t="n"/>
+      <c r="AF45" s="6" t="n"/>
+      <c r="AG45" s="6" t="n"/>
+      <c r="AH45" s="6" t="n"/>
+      <c r="AI45" s="6" t="n"/>
+      <c r="AJ45" s="6" t="n"/>
+      <c r="AK45" s="6" t="n"/>
+    </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="6" t="n"/>
@@ -3025,7 +3002,7 @@
       <c r="I46" s="6" t="n"/>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>TOTAL INTERNAL FREIGHT</t>
+          <t>TOTAL INSURANCE</t>
         </is>
       </c>
       <c r="K46" s="6" t="n"/>
@@ -3070,7 +3047,7 @@
       <c r="I47" s="6" t="n"/>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>TOTAL INSURANCE</t>
+          <t>TOTAL OTHER COST</t>
         </is>
       </c>
       <c r="K47" s="6" t="n"/>
@@ -3115,7 +3092,7 @@
       <c r="I48" s="6" t="n"/>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>TOTAL OTHER COST</t>
+          <t>TOTAL DEDUCTION</t>
         </is>
       </c>
       <c r="K48" s="6" t="n"/>
@@ -3160,7 +3137,7 @@
       <c r="I49" s="6" t="n"/>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>TOTAL DEDUCTION</t>
+          <t>ADJUSTMENTS</t>
         </is>
       </c>
       <c r="K49" s="6" t="n"/>
@@ -3168,10 +3145,14 @@
       <c r="M49" s="6" t="n"/>
       <c r="N49" s="6" t="n"/>
       <c r="O49" s="6" t="n"/>
-      <c r="P49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="7" t="n"/>
+      <c r="P49" s="7">
+        <f>(T35+U35+V35-W35)</f>
+        <v/>
+      </c>
+      <c r="Q49" s="7">
+        <f>(T35+U35+V35-W35)</f>
+        <v/>
+      </c>
       <c r="R49" s="6" t="n"/>
       <c r="S49" s="6" t="n"/>
       <c r="T49" s="6" t="n"/>
@@ -3193,56 +3174,55 @@
       <c r="AJ49" s="6" t="n"/>
       <c r="AK49" s="6" t="n"/>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="n"/>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
-      <c r="I50" s="6" t="n"/>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="K50" s="6" t="n"/>
-      <c r="L50" s="6" t="n"/>
-      <c r="M50" s="6" t="n"/>
-      <c r="N50" s="6" t="n"/>
-      <c r="O50" s="6" t="n"/>
-      <c r="P50" s="7">
-        <f>(T35+U35+V35-W35)</f>
-        <v/>
-      </c>
-      <c r="Q50" s="7">
-        <f>(T35+U35+V35-W35)</f>
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n"/>
-      <c r="S50" s="6" t="n"/>
-      <c r="T50" s="6" t="n"/>
-      <c r="U50" s="6" t="n"/>
-      <c r="V50" s="6" t="n"/>
-      <c r="W50" s="6" t="n"/>
-      <c r="X50" s="6" t="n"/>
-      <c r="Y50" s="6" t="n"/>
-      <c r="Z50" s="6" t="n"/>
-      <c r="AA50" s="6" t="n"/>
-      <c r="AB50" s="6" t="n"/>
-      <c r="AC50" s="6" t="n"/>
-      <c r="AD50" s="6" t="n"/>
-      <c r="AE50" s="6" t="n"/>
-      <c r="AF50" s="6" t="n"/>
-      <c r="AG50" s="6" t="n"/>
-      <c r="AH50" s="6" t="n"/>
-      <c r="AI50" s="6" t="n"/>
-      <c r="AJ50" s="6" t="n"/>
-      <c r="AK50" s="6" t="n"/>
-    </row>
-    <row r="51"/>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>NET TOTAL</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
+      <c r="N51" s="6" t="n"/>
+      <c r="O51" s="6" t="n"/>
+      <c r="P51" s="7">
+        <f>P41+P49</f>
+        <v/>
+      </c>
+      <c r="Q51" s="7">
+        <f>Q41+Q49</f>
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n"/>
+      <c r="S51" s="6" t="n"/>
+      <c r="T51" s="6" t="n"/>
+      <c r="U51" s="6" t="n"/>
+      <c r="V51" s="6" t="n"/>
+      <c r="W51" s="6" t="n"/>
+      <c r="X51" s="6" t="n"/>
+      <c r="Y51" s="6" t="n"/>
+      <c r="Z51" s="6" t="n"/>
+      <c r="AA51" s="6" t="n"/>
+      <c r="AB51" s="6" t="n"/>
+      <c r="AC51" s="6" t="n"/>
+      <c r="AD51" s="6" t="n"/>
+      <c r="AE51" s="6" t="n"/>
+      <c r="AF51" s="6" t="n"/>
+      <c r="AG51" s="6" t="n"/>
+      <c r="AH51" s="6" t="n"/>
+      <c r="AI51" s="6" t="n"/>
+      <c r="AJ51" s="6" t="n"/>
+      <c r="AK51" s="6" t="n"/>
+    </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="6" t="n"/>
@@ -3255,7 +3235,7 @@
       <c r="I52" s="6" t="n"/>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>NET TOTAL</t>
+          <t>INVOICE TOTAL</t>
         </is>
       </c>
       <c r="K52" s="6" t="n"/>
@@ -3264,13 +3244,10 @@
       <c r="N52" s="6" t="n"/>
       <c r="O52" s="6" t="n"/>
       <c r="P52" s="7">
-        <f>P42+P50</f>
-        <v/>
-      </c>
-      <c r="Q52" s="7">
-        <f>Q42+Q50</f>
-        <v/>
-      </c>
+        <f>S35</f>
+        <v/>
+      </c>
+      <c r="Q52" s="7" t="n"/>
       <c r="R52" s="6" t="n"/>
       <c r="S52" s="6" t="n"/>
       <c r="T52" s="6" t="n"/>
@@ -3292,145 +3269,142 @@
       <c r="AJ52" s="6" t="n"/>
       <c r="AK52" s="6" t="n"/>
     </row>
-    <row r="53">
-      <c r="A53" s="6" t="n"/>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="6" t="n"/>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="6" t="n"/>
-      <c r="I53" s="6" t="n"/>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>INVOICE TOTAL</t>
-        </is>
-      </c>
-      <c r="K53" s="6" t="n"/>
-      <c r="L53" s="6" t="n"/>
-      <c r="M53" s="6" t="n"/>
-      <c r="N53" s="6" t="n"/>
-      <c r="O53" s="6" t="n"/>
-      <c r="P53" s="7">
-        <f>S35</f>
-        <v/>
-      </c>
-      <c r="Q53" s="7" t="n"/>
-      <c r="R53" s="6" t="n"/>
-      <c r="S53" s="6" t="n"/>
-      <c r="T53" s="6" t="n"/>
-      <c r="U53" s="6" t="n"/>
-      <c r="V53" s="6" t="n"/>
-      <c r="W53" s="6" t="n"/>
-      <c r="X53" s="6" t="n"/>
-      <c r="Y53" s="6" t="n"/>
-      <c r="Z53" s="6" t="n"/>
-      <c r="AA53" s="6" t="n"/>
-      <c r="AB53" s="6" t="n"/>
-      <c r="AC53" s="6" t="n"/>
-      <c r="AD53" s="6" t="n"/>
-      <c r="AE53" s="6" t="n"/>
-      <c r="AF53" s="6" t="n"/>
-      <c r="AG53" s="6" t="n"/>
-      <c r="AH53" s="6" t="n"/>
-      <c r="AI53" s="6" t="n"/>
-      <c r="AJ53" s="6" t="n"/>
-      <c r="AK53" s="6" t="n"/>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="10" t="n"/>
-      <c r="B55" s="10" t="n"/>
-      <c r="C55" s="10" t="n"/>
-      <c r="D55" s="10" t="n"/>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="10" t="n"/>
-      <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n"/>
-      <c r="I55" s="10" t="n"/>
-      <c r="J55" s="10" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="10" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="inlineStr">
         <is>
           <t>VARIANCE CHECK</t>
         </is>
       </c>
-      <c r="K55" s="10" t="n"/>
-      <c r="L55" s="10" t="n"/>
-      <c r="M55" s="10" t="n"/>
-      <c r="N55" s="10" t="n"/>
-      <c r="O55" s="10" t="n"/>
-      <c r="P55" s="11">
-        <f>S35-P52</f>
-        <v/>
-      </c>
-      <c r="Q55" s="11">
-        <f>S35-Q52</f>
-        <v/>
-      </c>
-      <c r="R55" s="10" t="n"/>
-      <c r="S55" s="10" t="n"/>
-      <c r="T55" s="10" t="n"/>
-      <c r="U55" s="10" t="n"/>
-      <c r="V55" s="10" t="n"/>
-      <c r="W55" s="10" t="n"/>
-      <c r="X55" s="10" t="n"/>
-      <c r="Y55" s="10" t="n"/>
-      <c r="Z55" s="10" t="n"/>
-      <c r="AA55" s="10" t="n"/>
-      <c r="AB55" s="10" t="n"/>
-      <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="10" t="n"/>
-      <c r="AE55" s="10" t="n"/>
-      <c r="AF55" s="10" t="n"/>
-      <c r="AG55" s="10" t="n"/>
-      <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="10" t="n"/>
-      <c r="AJ55" s="10" t="n"/>
-      <c r="AK55" s="10" t="n"/>
-    </row>
-    <row r="56"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="11">
+        <f>S35-P51</f>
+        <v/>
+      </c>
+      <c r="Q54" s="11">
+        <f>S35-Q51</f>
+        <v/>
+      </c>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="10" t="n"/>
+      <c r="AF54" s="10" t="n"/>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n"/>
+      <c r="B56" s="12" t="n"/>
+      <c r="C56" s="12" t="n"/>
+      <c r="D56" s="12" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="12" t="n"/>
+      <c r="G56" s="12" t="n"/>
+      <c r="H56" s="12" t="n"/>
+      <c r="I56" s="12" t="n"/>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>DUTY ESTIMATION (Classification Cross-Check)</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="n"/>
+      <c r="L56" s="12" t="n"/>
+      <c r="M56" s="12" t="n"/>
+      <c r="N56" s="12" t="n"/>
+      <c r="O56" s="12" t="n"/>
+      <c r="P56" s="12" t="n"/>
+      <c r="Q56" s="12" t="n"/>
+      <c r="R56" s="12" t="n"/>
+      <c r="S56" s="12" t="n"/>
+      <c r="T56" s="12" t="n"/>
+      <c r="U56" s="12" t="n"/>
+      <c r="V56" s="12" t="n"/>
+      <c r="W56" s="12" t="n"/>
+      <c r="X56" s="12" t="n"/>
+      <c r="Y56" s="12" t="n"/>
+      <c r="Z56" s="12" t="n"/>
+      <c r="AA56" s="12" t="n"/>
+      <c r="AB56" s="12" t="n"/>
+      <c r="AC56" s="12" t="n"/>
+      <c r="AD56" s="12" t="n"/>
+      <c r="AE56" s="12" t="n"/>
+      <c r="AF56" s="12" t="n"/>
+      <c r="AG56" s="12" t="n"/>
+      <c r="AH56" s="12" t="n"/>
+      <c r="AI56" s="12" t="n"/>
+      <c r="AJ56" s="12" t="n"/>
+      <c r="AK56" s="12" t="n"/>
+    </row>
     <row r="57">
-      <c r="A57" s="12" t="n"/>
-      <c r="B57" s="12" t="n"/>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="n"/>
-      <c r="E57" s="12" t="n"/>
-      <c r="F57" s="12" t="n"/>
-      <c r="G57" s="12" t="n"/>
-      <c r="H57" s="12" t="n"/>
-      <c r="I57" s="12" t="n"/>
-      <c r="J57" s="12" t="inlineStr">
-        <is>
-          <t>DUTY ESTIMATION (Classification Cross-Check)</t>
-        </is>
-      </c>
-      <c r="K57" s="12" t="n"/>
-      <c r="L57" s="12" t="n"/>
-      <c r="M57" s="12" t="n"/>
-      <c r="N57" s="12" t="n"/>
-      <c r="O57" s="12" t="n"/>
-      <c r="P57" s="12" t="n"/>
-      <c r="Q57" s="12" t="n"/>
-      <c r="R57" s="12" t="n"/>
-      <c r="S57" s="12" t="n"/>
-      <c r="T57" s="12" t="n"/>
-      <c r="U57" s="12" t="n"/>
-      <c r="V57" s="12" t="n"/>
-      <c r="W57" s="12" t="n"/>
-      <c r="X57" s="12" t="n"/>
-      <c r="Y57" s="12" t="n"/>
-      <c r="Z57" s="12" t="n"/>
-      <c r="AA57" s="12" t="n"/>
-      <c r="AB57" s="12" t="n"/>
-      <c r="AC57" s="12" t="n"/>
-      <c r="AD57" s="12" t="n"/>
-      <c r="AE57" s="12" t="n"/>
-      <c r="AF57" s="12" t="n"/>
-      <c r="AG57" s="12" t="n"/>
-      <c r="AH57" s="12" t="n"/>
-      <c r="AI57" s="12" t="n"/>
-      <c r="AJ57" s="12" t="n"/>
-      <c r="AK57" s="12" t="n"/>
+      <c r="A57" s="13" t="n"/>
+      <c r="B57" s="13" t="n"/>
+      <c r="C57" s="13" t="n"/>
+      <c r="D57" s="13" t="n"/>
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="13" t="n"/>
+      <c r="G57" s="13" t="n"/>
+      <c r="H57" s="13" t="n"/>
+      <c r="I57" s="13" t="n"/>
+      <c r="J57" s="14" t="inlineStr">
+        <is>
+          <t>CIF (USD) = InvTotal + Freight + Insurance</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="n"/>
+      <c r="L57" s="13" t="n"/>
+      <c r="M57" s="13" t="n"/>
+      <c r="N57" s="13" t="n"/>
+      <c r="O57" s="13" t="n"/>
+      <c r="P57" s="15" t="n">
+        <v>128.93</v>
+      </c>
+      <c r="Q57" s="13" t="n"/>
+      <c r="R57" s="13" t="n"/>
+      <c r="S57" s="13" t="n"/>
+      <c r="T57" s="13" t="n"/>
+      <c r="U57" s="13" t="n"/>
+      <c r="V57" s="13" t="n"/>
+      <c r="W57" s="13" t="n"/>
+      <c r="X57" s="13" t="n"/>
+      <c r="Y57" s="13" t="n"/>
+      <c r="Z57" s="13" t="n"/>
+      <c r="AA57" s="13" t="n"/>
+      <c r="AB57" s="13" t="n"/>
+      <c r="AC57" s="13" t="n"/>
+      <c r="AD57" s="13" t="n"/>
+      <c r="AE57" s="13" t="n"/>
+      <c r="AF57" s="13" t="n"/>
+      <c r="AG57" s="13" t="n"/>
+      <c r="AH57" s="13" t="n"/>
+      <c r="AI57" s="13" t="n"/>
+      <c r="AJ57" s="13" t="n"/>
+      <c r="AK57" s="13" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="13" t="n"/>
@@ -3444,7 +3418,7 @@
       <c r="I58" s="13" t="n"/>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>CIF (USD) = InvTotal + Freight + Insurance</t>
+          <t>CIF (XCD) = CIF × 2.7169</t>
         </is>
       </c>
       <c r="K58" s="13" t="n"/>
@@ -3453,7 +3427,7 @@
       <c r="N58" s="13" t="n"/>
       <c r="O58" s="13" t="n"/>
       <c r="P58" s="15" t="n">
-        <v>128.93</v>
+        <v>350.29</v>
       </c>
       <c r="Q58" s="13" t="n"/>
       <c r="R58" s="13" t="n"/>
@@ -3489,7 +3463,7 @@
       <c r="I59" s="13" t="n"/>
       <c r="J59" s="14" t="inlineStr">
         <is>
-          <t>CIF (XCD) = CIF × 2.7169</t>
+          <t>CET (weighted avg 20.0%)</t>
         </is>
       </c>
       <c r="K59" s="13" t="n"/>
@@ -3498,7 +3472,7 @@
       <c r="N59" s="13" t="n"/>
       <c r="O59" s="13" t="n"/>
       <c r="P59" s="15" t="n">
-        <v>350.29</v>
+        <v>70.06</v>
       </c>
       <c r="Q59" s="13" t="n"/>
       <c r="R59" s="13" t="n"/>
@@ -3534,7 +3508,7 @@
       <c r="I60" s="13" t="n"/>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>CET (weighted avg 20.0%)</t>
+          <t xml:space="preserve">  └ 00000000: 20% CET (54% of value)</t>
         </is>
       </c>
       <c r="K60" s="13" t="n"/>
@@ -3543,7 +3517,7 @@
       <c r="N60" s="13" t="n"/>
       <c r="O60" s="13" t="n"/>
       <c r="P60" s="15" t="n">
-        <v>70.06</v>
+        <v>37.95</v>
       </c>
       <c r="Q60" s="13" t="n"/>
       <c r="R60" s="13" t="n"/>
@@ -3579,7 +3553,7 @@
       <c r="I61" s="13" t="n"/>
       <c r="J61" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 00000000: 20% CET (29% of value)</t>
+          <t xml:space="preserve">  └ 62046290: 20% CET (46% of value)</t>
         </is>
       </c>
       <c r="K61" s="13" t="n"/>
@@ -3588,7 +3562,7 @@
       <c r="N61" s="13" t="n"/>
       <c r="O61" s="13" t="n"/>
       <c r="P61" s="15" t="n">
-        <v>20.44</v>
+        <v>32.11</v>
       </c>
       <c r="Q61" s="13" t="n"/>
       <c r="R61" s="13" t="n"/>
@@ -3624,7 +3598,7 @@
       <c r="I62" s="13" t="n"/>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 62046290: 20% CET (46% of value)</t>
+          <t>CSC (6%)</t>
         </is>
       </c>
       <c r="K62" s="13" t="n"/>
@@ -3633,7 +3607,7 @@
       <c r="N62" s="13" t="n"/>
       <c r="O62" s="13" t="n"/>
       <c r="P62" s="15" t="n">
-        <v>32.11</v>
+        <v>21.02</v>
       </c>
       <c r="Q62" s="13" t="n"/>
       <c r="R62" s="13" t="n"/>
@@ -3669,7 +3643,7 @@
       <c r="I63" s="13" t="n"/>
       <c r="J63" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 85176200: 20% CET (25% of value)</t>
+          <t>VAT (15%) on CIF+CET+CSC</t>
         </is>
       </c>
       <c r="K63" s="13" t="n"/>
@@ -3678,7 +3652,7 @@
       <c r="N63" s="13" t="n"/>
       <c r="O63" s="13" t="n"/>
       <c r="P63" s="15" t="n">
-        <v>17.51</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="Q63" s="13" t="n"/>
       <c r="R63" s="13" t="n"/>
@@ -3703,49 +3677,49 @@
       <c r="AK63" s="13" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="n"/>
-      <c r="B64" s="13" t="n"/>
-      <c r="C64" s="13" t="n"/>
-      <c r="D64" s="13" t="n"/>
-      <c r="E64" s="13" t="n"/>
-      <c r="F64" s="13" t="n"/>
-      <c r="G64" s="13" t="n"/>
-      <c r="H64" s="13" t="n"/>
-      <c r="I64" s="13" t="n"/>
-      <c r="J64" s="14" t="inlineStr">
-        <is>
-          <t>CSC (6%)</t>
-        </is>
-      </c>
-      <c r="K64" s="13" t="n"/>
-      <c r="L64" s="13" t="n"/>
-      <c r="M64" s="13" t="n"/>
-      <c r="N64" s="13" t="n"/>
-      <c r="O64" s="13" t="n"/>
-      <c r="P64" s="15" t="n">
-        <v>21.02</v>
-      </c>
-      <c r="Q64" s="13" t="n"/>
-      <c r="R64" s="13" t="n"/>
-      <c r="S64" s="13" t="n"/>
-      <c r="T64" s="13" t="n"/>
-      <c r="U64" s="13" t="n"/>
-      <c r="V64" s="13" t="n"/>
-      <c r="W64" s="13" t="n"/>
-      <c r="X64" s="13" t="n"/>
-      <c r="Y64" s="13" t="n"/>
-      <c r="Z64" s="13" t="n"/>
-      <c r="AA64" s="13" t="n"/>
-      <c r="AB64" s="13" t="n"/>
-      <c r="AC64" s="13" t="n"/>
-      <c r="AD64" s="13" t="n"/>
-      <c r="AE64" s="13" t="n"/>
-      <c r="AF64" s="13" t="n"/>
-      <c r="AG64" s="13" t="n"/>
-      <c r="AH64" s="13" t="n"/>
-      <c r="AI64" s="13" t="n"/>
-      <c r="AJ64" s="13" t="n"/>
-      <c r="AK64" s="13" t="n"/>
+      <c r="A64" s="16" t="n"/>
+      <c r="B64" s="16" t="n"/>
+      <c r="C64" s="16" t="n"/>
+      <c r="D64" s="16" t="n"/>
+      <c r="E64" s="16" t="n"/>
+      <c r="F64" s="16" t="n"/>
+      <c r="G64" s="16" t="n"/>
+      <c r="H64" s="16" t="n"/>
+      <c r="I64" s="16" t="n"/>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>ESTIMATED TOTAL DUTIES</t>
+        </is>
+      </c>
+      <c r="K64" s="16" t="n"/>
+      <c r="L64" s="16" t="n"/>
+      <c r="M64" s="16" t="n"/>
+      <c r="N64" s="16" t="n"/>
+      <c r="O64" s="16" t="n"/>
+      <c r="P64" s="17" t="n">
+        <v>157.29</v>
+      </c>
+      <c r="Q64" s="16" t="n"/>
+      <c r="R64" s="16" t="n"/>
+      <c r="S64" s="16" t="n"/>
+      <c r="T64" s="16" t="n"/>
+      <c r="U64" s="16" t="n"/>
+      <c r="V64" s="16" t="n"/>
+      <c r="W64" s="16" t="n"/>
+      <c r="X64" s="16" t="n"/>
+      <c r="Y64" s="16" t="n"/>
+      <c r="Z64" s="16" t="n"/>
+      <c r="AA64" s="16" t="n"/>
+      <c r="AB64" s="16" t="n"/>
+      <c r="AC64" s="16" t="n"/>
+      <c r="AD64" s="16" t="n"/>
+      <c r="AE64" s="16" t="n"/>
+      <c r="AF64" s="16" t="n"/>
+      <c r="AG64" s="16" t="n"/>
+      <c r="AH64" s="16" t="n"/>
+      <c r="AI64" s="16" t="n"/>
+      <c r="AJ64" s="16" t="n"/>
+      <c r="AK64" s="16" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="13" t="n"/>
@@ -3759,7 +3733,7 @@
       <c r="I65" s="13" t="n"/>
       <c r="J65" s="14" t="inlineStr">
         <is>
-          <t>VAT (15%) on CIF+CET+CSC</t>
+          <t>Effective Duty Rate</t>
         </is>
       </c>
       <c r="K65" s="13" t="n"/>
@@ -3767,8 +3741,8 @@
       <c r="M65" s="13" t="n"/>
       <c r="N65" s="13" t="n"/>
       <c r="O65" s="13" t="n"/>
-      <c r="P65" s="15" t="n">
-        <v>66.20999999999999</v>
+      <c r="P65" s="18" t="n">
+        <v>0.4490279482714322</v>
       </c>
       <c r="Q65" s="13" t="n"/>
       <c r="R65" s="13" t="n"/>
@@ -3792,228 +3766,136 @@
       <c r="AJ65" s="13" t="n"/>
       <c r="AK65" s="13" t="n"/>
     </row>
-    <row r="66">
-      <c r="A66" s="16" t="n"/>
-      <c r="B66" s="16" t="n"/>
-      <c r="C66" s="16" t="n"/>
-      <c r="D66" s="16" t="n"/>
-      <c r="E66" s="16" t="n"/>
-      <c r="F66" s="16" t="n"/>
-      <c r="G66" s="16" t="n"/>
-      <c r="H66" s="16" t="n"/>
-      <c r="I66" s="16" t="n"/>
-      <c r="J66" s="12" t="inlineStr">
-        <is>
-          <t>ESTIMATED TOTAL DUTIES</t>
-        </is>
-      </c>
-      <c r="K66" s="16" t="n"/>
-      <c r="L66" s="16" t="n"/>
-      <c r="M66" s="16" t="n"/>
-      <c r="N66" s="16" t="n"/>
-      <c r="O66" s="16" t="n"/>
-      <c r="P66" s="17" t="n">
-        <v>157.29</v>
-      </c>
-      <c r="Q66" s="16" t="n"/>
-      <c r="R66" s="16" t="n"/>
-      <c r="S66" s="16" t="n"/>
-      <c r="T66" s="16" t="n"/>
-      <c r="U66" s="16" t="n"/>
-      <c r="V66" s="16" t="n"/>
-      <c r="W66" s="16" t="n"/>
-      <c r="X66" s="16" t="n"/>
-      <c r="Y66" s="16" t="n"/>
-      <c r="Z66" s="16" t="n"/>
-      <c r="AA66" s="16" t="n"/>
-      <c r="AB66" s="16" t="n"/>
-      <c r="AC66" s="16" t="n"/>
-      <c r="AD66" s="16" t="n"/>
-      <c r="AE66" s="16" t="n"/>
-      <c r="AF66" s="16" t="n"/>
-      <c r="AG66" s="16" t="n"/>
-      <c r="AH66" s="16" t="n"/>
-      <c r="AI66" s="16" t="n"/>
-      <c r="AJ66" s="16" t="n"/>
-      <c r="AK66" s="16" t="n"/>
-    </row>
     <row r="67">
-      <c r="A67" s="13" t="n"/>
-      <c r="B67" s="13" t="n"/>
-      <c r="C67" s="13" t="n"/>
-      <c r="D67" s="13" t="n"/>
-      <c r="E67" s="13" t="n"/>
-      <c r="F67" s="13" t="n"/>
-      <c r="G67" s="13" t="n"/>
-      <c r="H67" s="13" t="n"/>
-      <c r="I67" s="13" t="n"/>
-      <c r="J67" s="14" t="inlineStr">
-        <is>
-          <t>Effective Duty Rate</t>
-        </is>
-      </c>
-      <c r="K67" s="13" t="n"/>
-      <c r="L67" s="13" t="n"/>
-      <c r="M67" s="13" t="n"/>
-      <c r="N67" s="13" t="n"/>
-      <c r="O67" s="13" t="n"/>
-      <c r="P67" s="18" t="n">
-        <v>0.4490279482714322</v>
-      </c>
-      <c r="Q67" s="13" t="n"/>
-      <c r="R67" s="13" t="n"/>
-      <c r="S67" s="13" t="n"/>
-      <c r="T67" s="13" t="n"/>
-      <c r="U67" s="13" t="n"/>
-      <c r="V67" s="13" t="n"/>
-      <c r="W67" s="13" t="n"/>
-      <c r="X67" s="13" t="n"/>
-      <c r="Y67" s="13" t="n"/>
-      <c r="Z67" s="13" t="n"/>
-      <c r="AA67" s="13" t="n"/>
-      <c r="AB67" s="13" t="n"/>
-      <c r="AC67" s="13" t="n"/>
-      <c r="AD67" s="13" t="n"/>
-      <c r="AE67" s="13" t="n"/>
-      <c r="AF67" s="13" t="n"/>
-      <c r="AG67" s="13" t="n"/>
-      <c r="AH67" s="13" t="n"/>
-      <c r="AI67" s="13" t="n"/>
-      <c r="AJ67" s="13" t="n"/>
-      <c r="AK67" s="13" t="n"/>
-    </row>
-    <row r="68"/>
+      <c r="A67" s="20" t="n"/>
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="20" t="n"/>
+      <c r="E67" s="20" t="n"/>
+      <c r="F67" s="20" t="n"/>
+      <c r="G67" s="20" t="n"/>
+      <c r="H67" s="20" t="n"/>
+      <c r="I67" s="20" t="n"/>
+      <c r="J67" s="20" t="n"/>
+      <c r="K67" s="20" t="n"/>
+      <c r="L67" s="20" t="n"/>
+      <c r="M67" s="20" t="n"/>
+      <c r="N67" s="20" t="n"/>
+      <c r="O67" s="20" t="n"/>
+      <c r="P67" s="20" t="n"/>
+      <c r="Q67" s="20" t="n"/>
+      <c r="R67" s="20" t="n"/>
+      <c r="S67" s="20" t="n"/>
+      <c r="T67" s="20" t="n"/>
+      <c r="U67" s="20" t="n"/>
+      <c r="V67" s="20" t="n"/>
+      <c r="W67" s="20" t="n"/>
+      <c r="X67" s="20" t="n"/>
+      <c r="Y67" s="20" t="n"/>
+      <c r="Z67" s="20" t="n"/>
+      <c r="AA67" s="20" t="n"/>
+      <c r="AB67" s="20" t="n"/>
+      <c r="AC67" s="20" t="n"/>
+      <c r="AD67" s="20" t="n"/>
+      <c r="AE67" s="20" t="n"/>
+      <c r="AF67" s="20" t="n"/>
+      <c r="AG67" s="20" t="n"/>
+      <c r="AH67" s="20" t="n"/>
+      <c r="AI67" s="20" t="n"/>
+      <c r="AJ67" s="20" t="n"/>
+      <c r="AK67" s="20" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="20" t="n"/>
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="20" t="n"/>
+      <c r="E68" s="20" t="n"/>
+      <c r="F68" s="20" t="n"/>
+      <c r="G68" s="20" t="n"/>
+      <c r="H68" s="20" t="n"/>
+      <c r="I68" s="20" t="n"/>
+      <c r="J68" s="20" t="n"/>
+      <c r="K68" s="20" t="n"/>
+      <c r="L68" s="21" t="inlineStr">
+        <is>
+          <t>═══ COMBINED GRAND SUMMARY ═══</t>
+        </is>
+      </c>
+      <c r="M68" s="20" t="n"/>
+      <c r="N68" s="20" t="n"/>
+      <c r="O68" s="20" t="n"/>
+      <c r="P68" s="20" t="n"/>
+      <c r="Q68" s="20" t="n"/>
+      <c r="R68" s="20" t="n"/>
+      <c r="S68" s="20" t="n"/>
+      <c r="T68" s="20" t="n"/>
+      <c r="U68" s="20" t="n"/>
+      <c r="V68" s="20" t="n"/>
+      <c r="W68" s="20" t="n"/>
+      <c r="X68" s="20" t="n"/>
+      <c r="Y68" s="20" t="n"/>
+      <c r="Z68" s="20" t="n"/>
+      <c r="AA68" s="20" t="n"/>
+      <c r="AB68" s="20" t="n"/>
+      <c r="AC68" s="20" t="n"/>
+      <c r="AD68" s="20" t="n"/>
+      <c r="AE68" s="20" t="n"/>
+      <c r="AF68" s="20" t="n"/>
+      <c r="AG68" s="20" t="n"/>
+      <c r="AH68" s="20" t="n"/>
+      <c r="AI68" s="20" t="n"/>
+      <c r="AJ68" s="20" t="n"/>
+      <c r="AK68" s="20" t="n"/>
+    </row>
     <row r="69">
-      <c r="A69" s="20" t="n"/>
-      <c r="B69" s="20" t="n"/>
-      <c r="C69" s="20" t="n"/>
-      <c r="D69" s="20" t="n"/>
-      <c r="E69" s="20" t="n"/>
-      <c r="F69" s="20" t="n"/>
-      <c r="G69" s="20" t="n"/>
-      <c r="H69" s="20" t="n"/>
-      <c r="I69" s="20" t="n"/>
-      <c r="J69" s="20" t="n"/>
-      <c r="K69" s="20" t="n"/>
-      <c r="L69" s="20" t="n"/>
-      <c r="M69" s="20" t="n"/>
-      <c r="N69" s="20" t="n"/>
-      <c r="O69" s="20" t="n"/>
-      <c r="P69" s="20" t="n"/>
-      <c r="Q69" s="20" t="n"/>
-      <c r="R69" s="20" t="n"/>
-      <c r="S69" s="20" t="n"/>
-      <c r="T69" s="20" t="n"/>
-      <c r="U69" s="20" t="n"/>
-      <c r="V69" s="20" t="n"/>
-      <c r="W69" s="20" t="n"/>
-      <c r="X69" s="20" t="n"/>
-      <c r="Y69" s="20" t="n"/>
-      <c r="Z69" s="20" t="n"/>
-      <c r="AA69" s="20" t="n"/>
-      <c r="AB69" s="20" t="n"/>
-      <c r="AC69" s="20" t="n"/>
-      <c r="AD69" s="20" t="n"/>
-      <c r="AE69" s="20" t="n"/>
-      <c r="AF69" s="20" t="n"/>
-      <c r="AG69" s="20" t="n"/>
-      <c r="AH69" s="20" t="n"/>
-      <c r="AI69" s="20" t="n"/>
-      <c r="AJ69" s="20" t="n"/>
-      <c r="AK69" s="20" t="n"/>
+      <c r="L69" s="22" t="inlineStr">
+        <is>
+          <t>Invoice 1504495444</t>
+        </is>
+      </c>
+      <c r="P69" s="23" t="n">
+        <v>957.26</v>
+      </c>
+      <c r="Q69" s="24" t="n">
+        <v>-828.33</v>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="20" t="n"/>
-      <c r="B70" s="20" t="n"/>
-      <c r="C70" s="20" t="n"/>
-      <c r="D70" s="20" t="n"/>
-      <c r="E70" s="20" t="n"/>
-      <c r="F70" s="20" t="n"/>
-      <c r="G70" s="20" t="n"/>
-      <c r="H70" s="20" t="n"/>
-      <c r="I70" s="20" t="n"/>
-      <c r="J70" s="20" t="n"/>
-      <c r="K70" s="20" t="n"/>
-      <c r="L70" s="21" t="inlineStr">
-        <is>
-          <t>═══ COMBINED GRAND SUMMARY ═══</t>
-        </is>
-      </c>
-      <c r="M70" s="20" t="n"/>
-      <c r="N70" s="20" t="n"/>
-      <c r="O70" s="20" t="n"/>
-      <c r="P70" s="20" t="n"/>
-      <c r="Q70" s="20" t="n"/>
-      <c r="R70" s="20" t="n"/>
-      <c r="S70" s="20" t="n"/>
-      <c r="T70" s="20" t="n"/>
-      <c r="U70" s="20" t="n"/>
-      <c r="V70" s="20" t="n"/>
-      <c r="W70" s="20" t="n"/>
-      <c r="X70" s="20" t="n"/>
-      <c r="Y70" s="20" t="n"/>
-      <c r="Z70" s="20" t="n"/>
-      <c r="AA70" s="20" t="n"/>
-      <c r="AB70" s="20" t="n"/>
-      <c r="AC70" s="20" t="n"/>
-      <c r="AD70" s="20" t="n"/>
-      <c r="AE70" s="20" t="n"/>
-      <c r="AF70" s="20" t="n"/>
-      <c r="AG70" s="20" t="n"/>
-      <c r="AH70" s="20" t="n"/>
-      <c r="AI70" s="20" t="n"/>
-      <c r="AJ70" s="20" t="n"/>
-      <c r="AK70" s="20" t="n"/>
-    </row>
-    <row r="71">
-      <c r="L71" s="22" t="inlineStr">
-        <is>
-          <t>Invoice 1504495444</t>
-        </is>
-      </c>
-      <c r="P71" s="23" t="n">
-        <v>957.26</v>
-      </c>
-      <c r="Q71" s="24" t="n">
-        <v>-828.33</v>
+      <c r="L70" s="22" t="inlineStr">
+        <is>
+          <t>Invoice 15046495444</t>
+        </is>
+      </c>
+      <c r="P70" s="23" t="n">
+        <v>936.27</v>
+      </c>
+      <c r="Q70" s="24" t="n">
+        <v>-807.34</v>
       </c>
     </row>
     <row r="72">
-      <c r="L72" s="22" t="inlineStr">
-        <is>
-          <t>Invoice 15046495444</t>
-        </is>
-      </c>
-      <c r="P72" s="23" t="n">
-        <v>936.27</v>
-      </c>
-      <c r="Q72" s="24" t="n">
-        <v>-807.34</v>
-      </c>
-    </row>
-    <row r="73"/>
+      <c r="L72" s="25" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL</t>
+        </is>
+      </c>
+      <c r="P72" s="26" t="n">
+        <v>1893.53</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="L73" s="27" t="inlineStr">
+        <is>
+          <t>GRAND VARIANCE CHECK</t>
+        </is>
+      </c>
+      <c r="P73" s="24" t="n">
+        <v>-1635.67</v>
+      </c>
+    </row>
     <row r="74">
-      <c r="L74" s="25" t="inlineStr">
-        <is>
-          <t>GRAND TOTAL</t>
-        </is>
-      </c>
-      <c r="P74" s="26" t="n">
-        <v>1893.53</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="L75" s="27" t="inlineStr">
-        <is>
-          <t>GRAND VARIANCE CHECK</t>
-        </is>
-      </c>
-      <c r="P75" s="24" t="n">
-        <v>-1635.67</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="L76" s="28" t="inlineStr">
+      <c r="L74" s="28" t="inlineStr">
         <is>
           <t>Combined 2 invoice files</t>
         </is>
